--- a/data/reference/mappings/Mapping_Columns.xlsx
+++ b/data/reference/mappings/Mapping_Columns.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AA293A0-F275-496D-8979-D63985990365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD775BEC-ACAF-43E4-BEC1-F94DF58B942F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Bavaria - Precio Marzo_formul" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,11 @@
     <sheet name="Sell_Side_2026-ABI Mar 2026" sheetId="10" r:id="rId10"/>
     <sheet name="ABI 120326 -Pricing Marzo 2026" sheetId="11" r:id="rId11"/>
     <sheet name="Precios preformas FNC abril 202" sheetId="13" r:id="rId12"/>
-    <sheet name="MR PET Resin TLC" sheetId="12" r:id="rId13"/>
+    <sheet name="04.2026 - Preforsa" sheetId="14" r:id="rId13"/>
+    <sheet name="MR PET Resin TLC" sheetId="12" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'MR PET Resin TLC'!$A$1:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'MR PET Resin TLC'!$A$1:$C$23</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="140">
   <si>
     <t>metric_local</t>
   </si>
@@ -379,6 +380,27 @@
   </si>
   <si>
     <t>Precio reciclado r PET</t>
+  </si>
+  <si>
+    <t>ICIS N-1</t>
+  </si>
+  <si>
+    <t>FLETE MARITIMO</t>
+  </si>
+  <si>
+    <t>INTERNALIZATION COST</t>
+  </si>
+  <si>
+    <t>Internalization</t>
+  </si>
+  <si>
+    <t>OTHER COST ( CDP)</t>
+  </si>
+  <si>
+    <t>OTHER COST (BANK FEE)</t>
+  </si>
+  <si>
+    <t>VPET</t>
   </si>
   <si>
     <t>Raw Cost Breakdown</t>
@@ -1411,6 +1433,93 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45659B5-2CE2-47DA-BC38-CF41EB947CD4}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="25.28515625" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1422,7 +1531,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -1433,7 +1542,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1444,7 +1553,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -1466,7 +1575,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -1477,7 +1586,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -1488,7 +1597,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -1499,7 +1608,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -1510,7 +1619,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -1521,7 +1630,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -1532,7 +1641,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
@@ -1543,7 +1652,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -1554,7 +1663,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1565,7 +1674,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
@@ -1576,7 +1685,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
@@ -1587,7 +1696,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -1598,7 +1707,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
         <v>86</v>
@@ -1609,7 +1718,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
@@ -1620,7 +1729,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
@@ -1631,7 +1740,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1642,7 +1751,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
@@ -1653,7 +1762,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
         <v>68</v>
@@ -1664,7 +1773,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
         <v>64</v>
